--- a/services/integrator/internal/document/testdata/stok-nilai-q1-2026.golden.xlsx
+++ b/services/integrator/internal/document/testdata/stok-nilai-q1-2026.golden.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">PT Stok Uji</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t xml:space="preserve">Gula Aren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Manis</t>
   </si>
   <si>
     <t xml:space="preserve">B001</t>
@@ -446,28 +452,22 @@
         <v>17</v>
       </c>
       <c r="D10" s="7">
-        <v>7.625</v>
-      </c>
-      <c r="E10" s="8">
-        <v>648128.81</v>
+        <v>0</v>
       </c>
       <c r="F10" s="7">
-        <v>6.375</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="8">
-        <v>443625</v>
+        <v>1</v>
       </c>
       <c r="H10" s="7">
-        <v>4.334</v>
-      </c>
-      <c r="I10" s="8">
-        <v>376842.77</v>
+        <v>0</v>
       </c>
       <c r="J10" s="7">
-        <v>9.666</v>
+        <v>0.5</v>
       </c>
       <c r="K10" s="8">
-        <v>840461.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -475,40 +475,43 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="7">
-        <v>0</v>
+        <v>7.625</v>
+      </c>
+      <c r="E11" s="8">
+        <v>648128.81</v>
       </c>
       <c r="F11" s="7">
-        <v>7</v>
+        <v>6.375</v>
       </c>
       <c r="G11" s="8">
-        <v>210000</v>
+        <v>443625</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>4.334</v>
       </c>
       <c r="I11" s="8">
-        <v>210000</v>
+        <v>376842.77</v>
       </c>
       <c r="J11" s="7">
-        <v>0</v>
+        <v>9.666</v>
       </c>
       <c r="K11" s="8">
-        <v>0</v>
+        <v>840461.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
@@ -516,19 +519,22 @@
         <v>0</v>
       </c>
       <c r="F12" s="7">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="G12" s="8">
-        <v>304500</v>
+        <v>210000</v>
       </c>
       <c r="H12" s="7">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I12" s="8">
+        <v>210000</v>
       </c>
       <c r="J12" s="7">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K12" s="8">
-        <v>304500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -545,13 +551,19 @@
         <v>0</v>
       </c>
       <c r="F13" s="7">
-        <v>1</v>
+        <v>2.9</v>
+      </c>
+      <c r="G13" s="8">
+        <v>304500</v>
       </c>
       <c r="H13" s="7">
         <v>0</v>
       </c>
       <c r="J13" s="7">
-        <v>1</v>
+        <v>2.9</v>
+      </c>
+      <c r="K13" s="8">
+        <v>304500</v>
       </c>
     </row>
     <row r="14">
@@ -562,83 +574,74 @@
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D14" s="7">
         <v>0</v>
       </c>
       <c r="F14" s="7">
-        <v>0.30000000000000004</v>
+        <v>1</v>
       </c>
       <c r="H14" s="7">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="7">
-        <v>5.551115123125783e-17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
         <v>32</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>33</v>
       </c>
-      <c r="C15" t="s">
-        <v>34</v>
-      </c>
       <c r="D15" s="7">
         <v>0</v>
       </c>
       <c r="F15" s="7">
-        <v>2</v>
-      </c>
-      <c r="G15" s="8">
-        <v>50000</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="H15" s="7">
-        <v>5.5</v>
-      </c>
-      <c r="I15" s="8">
-        <v>137500</v>
+        <v>0.3</v>
       </c>
       <c r="J15" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="K15" s="8">
-        <v>-87500</v>
+        <v>5.551115123125783e-17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
       <c r="D16" s="7">
         <v>0</v>
       </c>
       <c r="F16" s="7">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G16" s="8">
-        <v>300</v>
+        <v>50000</v>
       </c>
       <c r="H16" s="7">
-        <v>0.3</v>
+        <v>5.5</v>
       </c>
       <c r="I16" s="8">
-        <v>300</v>
+        <v>137500</v>
       </c>
       <c r="J16" s="7">
-        <v>0.2</v>
+        <v>-3.5</v>
       </c>
       <c r="K16" s="8">
-        <v>200</v>
+        <v>-87500</v>
       </c>
     </row>
     <row r="17">
@@ -649,31 +652,28 @@
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D17" s="7">
-        <v>1.25</v>
-      </c>
-      <c r="E17" s="8">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="F17" s="7">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="8">
-        <v>229000.96</v>
+        <v>300</v>
       </c>
       <c r="H17" s="7">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="I17" s="8">
-        <v>77248.26</v>
+        <v>300</v>
       </c>
       <c r="J17" s="7">
-        <v>4.6499999999999995</v>
+        <v>0.2</v>
       </c>
       <c r="K17" s="8">
-        <v>211296.7</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18">
@@ -684,64 +684,99 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D18" s="7">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E18" s="8">
+        <v>55000</v>
       </c>
       <c r="F18" s="7">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="G18" s="8">
-        <v>4.02</v>
+        <v>229000.96</v>
       </c>
       <c r="H18" s="7">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="I18" s="8">
-        <v>1</v>
+        <v>77248.26</v>
       </c>
       <c r="J18" s="7">
-        <v>3</v>
+        <v>4.6499999999999995</v>
       </c>
       <c r="K18" s="8">
-        <v>3</v>
+        <v>211296.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>43</v>
       </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
       <c r="D19" s="7">
         <v>0</v>
       </c>
       <c r="F19" s="7">
+        <v>4</v>
+      </c>
+      <c r="G19" s="8">
+        <v>4.02</v>
+      </c>
+      <c r="H19" s="7">
         <v>1</v>
       </c>
-      <c r="H19" s="7">
-        <v>0</v>
+      <c r="I19" s="8">
+        <v>1.01</v>
       </c>
       <c r="J19" s="7">
+        <v>3</v>
+      </c>
+      <c r="K19" s="8">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="K20" s="10">
-        <v>10033886.68</v>
+      <c r="H20" s="7">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
-        <v>45</v>
+      <c r="B21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K21" s="10">
+        <v>10033887.71</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
